--- a/practice-files/day04-数据清洗.xlsx
+++ b/practice-files/day04-数据清洗.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="练习说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="脏数据" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="脏数据" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -561,19 +560,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/practice-files/day04-数据清洗.xlsx
+++ b/practice-files/day04-数据清洗.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -499,51 +499,65 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>WPS提示：WPS里在"数据"选项卡的"重复项"组里找"删除重复项"，还可先试试"高亮重复项"</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>【练习2：文本分列】</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>【练习2：文本分列】</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>A列"用户ID-日期"是合并的→数据→分列→按分隔符"-" 拆成两列</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>【练习3：查找替换】</t>
+          <t>WPS提示：WPS里同样在"数据"选项卡→分列，流程一样</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>1. 把多余的空格删掉（C列有些名字前后有空格）</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2. D列有些单元格里有换行符（Alt+Enter产生的），用查找替换清理</t>
+          <t>【练习3：查找替换】</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>1. 把多余的空格删掉（C列有些名字前后有空格）</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2. D列有些单元格里有换行符（Alt+Enter产生的），用查找替换清理</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>【注意】操作前先把"脏数据"工作表复制一份（右键标签→移动或复制→建立副本），防止改坏了没法恢复。</t>
         </is>

--- a/practice-files/day04-数据清洗.xlsx
+++ b/practice-files/day04-数据清洗.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,22 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00E67E22"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="002E7D32"/>
       <sz val="10.5"/>
     </font>
     <font>
@@ -86,16 +102,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -560,6 +581,41 @@
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>【注意】操作前先把"脏数据"工作表复制一份（右键标签→移动或复制→建立副本），防止改坏了没法恢复。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>思考题1: 去重时勾一列和勾两列的区别？给发奖名单去重应该勾什么？</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" hidden="1" outlineLevel="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>💡 答案: 勾一列=该列内容重复就删（同一用户的多条记录会被误删）；勾两列=两列同时相同才视为重复。发奖名单按"用户ID"单列去重。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>思考题2: 为什么去重和替换之前一定要先复制一份原始数据？</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" hidden="1" outlineLevel="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>💡 答案: 这两个操作不可逆，发奖励场景删错了是真金白银的损失。"动刀前先备份"是数据分析的第一条职业习惯。</t>
         </is>
       </c>
     </row>
@@ -584,40 +640,40 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>用户ID-日期（需分列）</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>用户ID（分列结果）</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>用户姓名（有多余空格）</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>备注（有换行符）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>U1001-20260315</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> 张三 </t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>第一行
 备注内容</t>
@@ -625,36 +681,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>U1002-20260316</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>李  四</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>正常备注</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>U1001-20260315</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr"/>
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> 张三 </t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>第一行
 备注内容</t>
@@ -662,18 +718,18 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>U1003-20260317</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  王五  </t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>有
 换行
@@ -682,36 +738,36 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>U1004-20260318</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr"/>
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>赵六</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>U1003-20260317</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  王五  </t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>有
 换行
@@ -720,36 +776,36 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>U1005-20260319</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr"/>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr"/>
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> 孙 七 </t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>正常备注</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>U1006-20260320</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  周八</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>带
 多行
@@ -758,36 +814,36 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>U1007-20260321</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr"/>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr"/>
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> 吴九</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>U1008-20260322</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  郑十  </t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>又有一个
 换行符</t>
@@ -795,54 +851,54 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>U1005-20260319</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr"/>
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> 孙 七 </t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>正常备注</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>U1009-20260323</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr"/>
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>钱十一</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>U1010-20260324</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr"/>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr"/>
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  冯十二  </t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">末尾也有换行
 </t>

--- a/practice-files/day04-数据清洗.xlsx
+++ b/practice-files/day04-数据清洗.xlsx
@@ -587,7 +587,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>📝 思考题（先自己想想，点左侧+号展开答案）</t>
+          <t>思考题（先自己想想，点左侧+号展开答案）</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <row r="21" hidden="1" outlineLevel="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: 勾一列=该列内容重复就删（同一用户的多条记录会被误删）；勾两列=两列同时相同才视为重复。发奖名单按"用户ID"单列去重。</t>
+          <t>答案: 勾一列=该列内容重复就删（同一用户的多条记录会被误删）；勾两列=两列同时相同才视为重复。发奖名单按"用户ID"单列去重。</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
     <row r="24" hidden="1" outlineLevel="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>💡 答案: 这两个操作不可逆，发奖励场景删错了是真金白银的损失。"动刀前先备份"是数据分析的第一条职业习惯。</t>
+          <t>答案: 这两个操作不可逆，发奖励场景删错了是真金白银的损失。"动刀前先备份"是数据分析的第一条职业习惯。</t>
         </is>
       </c>
     </row>

--- a/practice-files/day04-数据清洗.xlsx
+++ b/practice-files/day04-数据清洗.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="练习说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="脏数据" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="活动参与名单(备用实战)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -580,40 +581,47 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>【备用实战】"活动参与名单(备用实战)"工作表模拟活动回复用户列表（含重复用户），练去重用</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>【注意】操作前先把"脏数据"工作表复制一份（右键标签→移动或复制→建立副本），防止改坏了没法恢复。</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>思考题（先自己想想，点左侧+号展开答案）</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>思考题1: 去重时勾一列和勾两列的区别？给发奖名单去重应该勾什么？</t>
         </is>
       </c>
     </row>
-    <row r="21" hidden="1" outlineLevel="1">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="22" hidden="1" outlineLevel="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>答案: 勾一列=该列内容重复就删（同一用户的多条记录会被误删）；勾两列=两列同时相同才视为重复。发奖名单按"用户ID"单列去重。</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>思考题2: 为什么去重和替换之前一定要先复制一份原始数据？</t>
         </is>
       </c>
     </row>
-    <row r="24" hidden="1" outlineLevel="1">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="25" hidden="1" outlineLevel="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>答案: 这两个操作不可逆，发奖励场景删错了是真金白银的损失。"动刀前先备份"是数据分析的第一条职业习惯。</t>
         </is>
@@ -908,4 +916,882 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>用户ID</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>昵称</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>参与活动</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>参与日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>U1004</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>柚子</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>618年中庆</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>U1007</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>小鱼</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>双11狂欢</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>U1006</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>麦子</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>端午打卡</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>U1011</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>奶茶</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>春节福袋</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>U1001</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>石头</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>端午打卡</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>U1004</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>柠檬茶</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>元旦集卡</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>U1005</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>白鹿</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>春节福袋</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>U1001</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>浮云</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>圣诞竞拍夜</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>U1004</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>夏夜</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>520告白季</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>U1006</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>夏夜</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>圣诞竞拍夜</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>U1011</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>夜风</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>618年中庆</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>U1007</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>麦子</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>春节福袋</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>U1008</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>山川</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>520告白季</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>U1011</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>奶茶</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>端午打卡</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>U1007</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>麦子</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>520告白季</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>U1008</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>柠檬茶</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>元旦集卡</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>U1011</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>石头</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>春节福袋</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>U1006</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>大树</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>520告白季</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>U1009</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>星星</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>端午打卡</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>U1004</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>海盐</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>618年中庆</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>U1010</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>小鱼</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>双11狂欢</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>U1009</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>麦子</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>618年中庆</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>U1011</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>小鱼</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>520告白季</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>U1004</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>落落</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>双11狂欢</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>U1005</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>阿明</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>520告白季</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>U1002</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>柠檬茶</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>圣诞竞拍夜</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>U1006</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>月亮</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>端午打卡</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>U1009</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>大树</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>端午打卡</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>U1011</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>月亮</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>双11狂欢</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>U1001</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>阿明</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>圣诞竞拍夜</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>U1011</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>夜风</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>圣诞竞拍夜</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>U1002</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>海盐</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>端午打卡</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>U1003</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>麦子</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>端午打卡</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>U1010</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>月亮</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>双11狂欢</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>U1009</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>大树</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>端午打卡</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>U1005</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>白鹿</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>春节福袋</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>U1001</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>浮云</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>圣诞竞拍夜</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>U1011</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>奶茶</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>端午打卡</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/practice-files/day04-数据清洗.xlsx
+++ b/practice-files/day04-数据清洗.xlsx
@@ -958,100 +958,100 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>U1004</t>
+          <t>U1011</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>柚子</t>
+          <t>奶茶</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>618年中庆</t>
+          <t>春节福袋</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>U1007</t>
+          <t>U1004</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>小鱼</t>
+          <t>夜风</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>双11狂欢</t>
+          <t>618年中庆</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>U1006</t>
+          <t>U1011</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>麦子</t>
+          <t>星星</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>端午打卡</t>
+          <t>元旦集卡</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-01-02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1006</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>奶茶</t>
+          <t>大树</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>春节福袋</t>
+          <t>520告白季</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>U1001</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>石头</t>
+          <t>星星</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1073,73 +1073,73 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>柠檬茶</t>
+          <t>海盐</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>元旦集卡</t>
+          <t>618年中庆</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>U1005</t>
+          <t>U1010</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>白鹿</t>
+          <t>小鱼</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>春节福袋</t>
+          <t>双11狂欢</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>U1001</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>浮云</t>
+          <t>麦子</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>圣诞竞拍夜</t>
+          <t>618年中庆</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>U1004</t>
+          <t>U1011</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>夏夜</t>
+          <t>小鱼</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -1149,107 +1149,107 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-01-12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>U1006</t>
+          <t>U1004</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>夏夜</t>
+          <t>落落</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>圣诞竞拍夜</t>
+          <t>双11狂欢</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-01-06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1005</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>夜风</t>
+          <t>阿明</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>618年中庆</t>
+          <t>520告白季</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>U1007</t>
+          <t>U1002</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>麦子</t>
+          <t>柠檬茶</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>春节福袋</t>
+          <t>圣诞竞拍夜</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>U1008</t>
+          <t>U1006</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>山川</t>
+          <t>月亮</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>520告白季</t>
+          <t>端午打卡</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-02-15</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>奶茶</t>
+          <t>大树</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -1259,51 +1259,51 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-01-24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>U1007</t>
+          <t>U1011</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>麦子</t>
+          <t>月亮</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>520告白季</t>
+          <t>双11狂欢</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>U1008</t>
+          <t>U1001</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>柠檬茶</t>
+          <t>阿明</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>元旦集卡</t>
+          <t>圣诞竞拍夜</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -1315,51 +1315,51 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>石头</t>
+          <t>夜风</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>春节福袋</t>
+          <t>圣诞竞拍夜</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>U1006</t>
+          <t>U1002</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>大树</t>
+          <t>海盐</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>520告白季</t>
+          <t>端午打卡</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>U1009</t>
+          <t>U1003</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>星星</t>
+          <t>麦子</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1369,29 +1369,29 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>U1004</t>
+          <t>U1010</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>海盐</t>
+          <t>月亮</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>618年中庆</t>
+          <t>双11狂欢</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1403,237 +1403,237 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>小鱼</t>
+          <t>白鹿</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>双11狂欢</t>
+          <t>春节福袋</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-28</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>U1009</t>
+          <t>U1011</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>麦子</t>
+          <t>夏夜</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>618年中庆</t>
+          <t>元旦集卡</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1008</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>小鱼</t>
+          <t>大树</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>520告白季</t>
+          <t>圣诞竞拍夜</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>U1004</t>
+          <t>U1008</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>落落</t>
+          <t>柚子</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>双11狂欢</t>
+          <t>圣诞竞拍夜</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-02-11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>U1005</t>
+          <t>U1007</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>阿明</t>
+          <t>海盐</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>520告白季</t>
+          <t>元旦集卡</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>U1002</t>
+          <t>U1003</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>柠檬茶</t>
+          <t>风筝</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>圣诞竞拍夜</t>
+          <t>春节福袋</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>U1006</t>
+          <t>U1002</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>月亮</t>
+          <t>柠檬茶</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>端午打卡</t>
+          <t>圣诞竞拍夜</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>U1009</t>
+          <t>U1012</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>大树</t>
+          <t>奶茶</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>端午打卡</t>
+          <t>618年中庆</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1001</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>月亮</t>
+          <t>落落</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>双11狂欢</t>
+          <t>端午打卡</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>U1001</t>
+          <t>U1002</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>阿明</t>
+          <t>白鹿</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>圣诞竞拍夜</t>
+          <t>双11狂欢</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1012</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>夜风</t>
+          <t>阿明</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>圣诞竞拍夜</t>
+          <t>双11狂欢</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>海盐</t>
+          <t>落落</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -1655,129 +1655,129 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-04-05</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>U1003</t>
+          <t>U1011</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>麦子</t>
+          <t>风筝</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>端午打卡</t>
+          <t>520告白季</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-02-12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>U1010</t>
+          <t>U1009</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>月亮</t>
+          <t>奶茶</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>双11狂欢</t>
+          <t>春节福袋</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>U1009</t>
+          <t>U1011</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>大树</t>
+          <t>月亮</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>端午打卡</t>
+          <t>双11狂欢</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>U1005</t>
+          <t>U1012</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>白鹿</t>
+          <t>奶茶</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>春节福袋</t>
+          <t>618年中庆</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-18</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>U1001</t>
+          <t>U1004</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>浮云</t>
+          <t>夜风</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>圣诞竞拍夜</t>
+          <t>618年中庆</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>U1011</t>
+          <t>U1002</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>奶茶</t>
+          <t>海盐</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
